--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260911.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260911.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.84%</t>
+          <t>26.72%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>99,790</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>8.24%</t>
+          <t>8.05%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,685</t>
+          <t>99,790</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.82%</t>
+          <t>8.04%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6.22%</t>
+          <t>6.42%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.38%</t>
+          <t>5.34%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.23%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.17%</t>
+          <t>3.19%</t>
         </is>
       </c>
     </row>
@@ -770,51 +770,51 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.05%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NET US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Cloudflare公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>18,283</t>
+          <t>19,725</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.07%</t>
+          <t>3.01%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>NET US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>Cloudflare公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>19,725</t>
+          <t>18,283</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.04%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.91%</t>
+          <t>2.89%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.29%</t>
+          <t>2.56%</t>
         </is>
       </c>
     </row>
@@ -880,7 +880,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.09%</t>
+          <t>2.08%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.75%</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.49%</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.41%</t>
         </is>
       </c>
     </row>
@@ -1034,24 +1034,24 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ED US</t>
+          <t>ALAB US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>聯合愛迪生</t>
+          <t>Astera實驗室公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>21,308</t>
+          <t>7,890</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
@@ -1063,22 +1063,22 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>ALAB US</t>
+          <t>ED US</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Astera實驗室公司</t>
+          <t>聯合愛迪生</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>7,890</t>
+          <t>21,308</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.87%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1210,51 +1210,51 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>PPL US</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>PPL Corp</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>37,340</t>
+          <t>42,930</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>PPL US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PPL Corp</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>42,930</t>
+          <t>37,340</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.78%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.43%</t>
         </is>
       </c>
     </row>
